--- a/光伏配储项目/电价数据/2026/上华站.xlsx
+++ b/光伏配储项目/电价数据/2026/上华站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.32824</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.68199</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07534</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.74405</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.6297999999999999</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17309</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26926</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25436</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25896</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24365</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.63252</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6293500000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.60568</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.82751</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.2433</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40127</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44268</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9198</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5861900000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.36144</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.69704</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.06137</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.06285</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.44023</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.38174</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45907</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.73714</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.80604</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.59397</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.76071</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.7694099999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7928500000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.69916</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.45516</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.391</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.64825</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.07919</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.84348</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.69739</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.6338400000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.41218</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.42022</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4049700000000001</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5097699999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.56209</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.55674</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6674099999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6285700000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.94052</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.84494</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.78116</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5484</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.44266</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.74499</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.73717</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.40556</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.54492</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.33434</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.52128</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.08068</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.50594</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.46708</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.36053</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.27358</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.22985</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.00663</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.42291</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.15834</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.49095</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>1.01596</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.88876</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.48737</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.45988</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.48056</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3305</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.46708</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.40826</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.16899</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.20579</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28366</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.12923</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.9374600000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.75651</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.74463</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.12913</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.12715</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>1.19967</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.12657</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.49808</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.78499</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.79823</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.81663</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.11555</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.61729</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.69929</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>1.1966</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.12079</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.78925</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8868400000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5791799999999999</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.24967</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.61642</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.43138</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51388</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.58256</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.9564199999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.02652</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.8097799999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.73288</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.70452</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70241</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.5302100000000001</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.57001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.67762</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.9182</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.81196</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.65758</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48722</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.69056</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.50282</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.75288</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.0708</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.30522</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.82924</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.47105</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8793500000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.6566799999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5818099999999999</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.72825</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.46621</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.49227</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.33773</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.44342</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.41434</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.45607</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44255</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.56409</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.90459</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46456</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.41406</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.76376</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.46478</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.43173</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.49656</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.88478</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.6589400000000001</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.50491</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.46588</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.6803899999999999</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.41006</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.05132</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.60986</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.89559</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.80445</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.5574</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.59678</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.69885</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.62895</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66379</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6688999999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.64195</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.55031</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.50356</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.48907</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.42117</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14337</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02407</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.46985</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26672</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25727</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24106</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10613</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02943</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26344</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.42203</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42302</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31695</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.44791</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23923</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24581</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19036</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.20554</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24792</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.21152</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24758</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21392</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19167</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17297</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24844</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26994</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26673</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09209999999999999</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2061</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04921</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19385</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.009259999999999999</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06025</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05845</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31561</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.50195</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.43648</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.5007200000000001</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.48794</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7896299999999999</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8703099999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6533600000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5720499999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.46815</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.60022</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.64471</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.9710800000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.5825900000000001</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.79306</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.02885</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.43122</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.81089</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.65462</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17799</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26191</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26149</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28058</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32322</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.81238</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.49173</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.64489</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.53287</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2392</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.58039</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.6018300000000001</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.48291</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.45166</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.51873</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.50305</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.68713</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.55331</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.51201</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.55796</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.55347</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.52346</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.58145</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.32887</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.25088</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.71902</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.8710399999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.52767</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.7840900000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.42085</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.25805</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.28024</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.59061</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.25969</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.40203</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.49715</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.48346</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.17717</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.02284</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.48432</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.45507</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33153</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.21294</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.22354</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18568</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.21908</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18292</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.18593</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.26992</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.44446</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04417</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18521</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.04713000000000001</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.21852</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.19283</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23188</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.24437</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26977</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26989</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.43379</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.4157</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24815</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28057</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28891</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28207</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30154</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28478</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24583</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.43642</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30319</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.04233</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.64579</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4831</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48862</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43308</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.49049</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42621</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.54388</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.45795</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.47263</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.79927</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.62709</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43432</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41327</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5322</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.45269</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.42091</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.5121599999999999</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.49278</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.58975</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.81577</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.43799</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.55698</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.54692</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69529</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46257</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.5022099999999999</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28442</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31432</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.28042</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28066</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19742</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18972</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27392</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27845</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27357</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19151</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18887</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.15231</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23451</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26167</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19432</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20102</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16523</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.15671</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.24329</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.25652</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.43163</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38629</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.43338</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.45946</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.26196</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27885</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27309</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.25469</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.25979</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23341</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32087</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28014</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.01972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28249</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.2830299999999999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27363</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28347</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.58296</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5166000000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.20325</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29629</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49652</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.61166</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5748</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6204400000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7624500000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4771</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31386</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44871</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42203</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44093</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47222</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.51103</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5758300000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.44768</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41269</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6499400000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.70325</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48374</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49461</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.43368</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.67769</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5532699999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64228</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31468</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26462</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28593</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.005849999999999999</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27483</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28314</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.51291</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.5280499999999999</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.5466799999999999</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.5788</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.52252</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41784</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.41886</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.51189</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.54104</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.27532</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.35628</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.26011</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16495</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.00744</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.27303</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.01023</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.009689999999999999</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.16518</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.02134</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19852</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.16397</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.01021</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15466</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15915</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19444</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15681</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.16219</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.01073</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16487</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.01085</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.03623</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17565</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18044</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.14722</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.04071</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.17946</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.27148</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.57811</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>8.000000000000001e-05</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.40543</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24939</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21773</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24402</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.27231</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.27058</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.2266</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.23158</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.27248</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.2203</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.24577</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34474</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22776</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27219</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.03775999999999999</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18296</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18002</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.2656</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.02015</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19995</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22117</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21273</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.02577</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.03196</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.01792</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.01826</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.01826</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.01805</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19457</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.01826</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.01824</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17316</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.03196</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.03195</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.01719</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.01639</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24394</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.02322</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00774</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.2662</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02206</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-4e-05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.03058</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.0194</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.07238</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.02783</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.01731</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26772</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.00265</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.16591</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16101</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16533</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.16275</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.04385</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15887</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.14796</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.04351</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.04442</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.04361</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.01296</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.01152</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.00907</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.4143</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18939</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.04411</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.23281</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85722</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86226</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09026000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.01738</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24714</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.52703</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00177</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06920999999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47528</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.63251</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50312</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.74024</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.57429</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.42229</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.72651</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.7426799999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.74091</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.74442</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.82739</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30646</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44823</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28814</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.26776</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26187</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.18726</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25735</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24544</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.25335</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19943</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.16375</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.19506</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.15834</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.16098</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.04442</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.15372</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17828</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.22892</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23832</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24741</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25115</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27442</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25863</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29021</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5474199999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41443</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.45455</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.20465</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7477999999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7591599999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.51435</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6435299999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.78713</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40823</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.53815</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19991</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31557</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.48596</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.49744</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.98581</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.75797</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.52901</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6688099999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46051</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5430499999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49445</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6434</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.60563</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.92399</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.75517</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.65935</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55647</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32018</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28221</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26653</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42719</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.54979</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19883</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.40487</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.51888</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.50451</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.52927</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.7131000000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.71775</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.73325</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.57316</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44351</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.5301900000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.45541</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32411</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.66244</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.43738</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27698</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.45128</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.9054</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.93986</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.58877</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.73888</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.01674</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.43164</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.61909</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.67427</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40696</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41637</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4933999999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41484</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43132</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33768</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17611</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14577</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19867</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14655</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04787</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12175</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22625</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26017</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14353</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18771</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22686</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.21141</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.22745</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.24808</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.22326</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.47574</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.4637</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.47008</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.87898</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.00201</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.6476799999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.74625</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.71827</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.8152699999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.50706</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.47804</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.54386</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.88983</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.75637</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.95721</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.48876</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>1.01233</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.47288</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.91452</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.47714</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.86553</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.90712</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.70604</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.48388</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.47512</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.45354</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36765</v>
       </c>
     </row>
   </sheetData>
